--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,37 +43,38 @@
     <t>Path</t>
   </si>
   <si>
-    <t>SEBI</t>
-  </si>
-  <si>
-    <t>IFSCA</t>
+    <t>IBBI</t>
+  </si>
+  <si>
+    <t>Discussion Paper</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
   <si>
     <t>February</t>
   </si>
   <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFSCA (Fund Management) (Amendment) Regulations, 2026
-</t>
-  </si>
-  <si>
-    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=36ff47aaeb9222f627d166fe86841979&amp;fileName=106_IFSCA__Fund_Management___Amendment__Regulations__2026_20260202_0720.pdf</t>
-  </si>
-  <si>
-    <t>106_IFSCA__Fund_Management___Amendment__Regulations__2026_20260202_0720.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Regulations/2026/February/106_IFSCA__Fund_Management___Amendment__Regulations__2026_20260202_0720.pdf</t>
+    <t>2026-02-16</t>
+  </si>
+  <si>
+    <t>Discussion paper – Process Division - February 2026</t>
+  </si>
+  <si>
+    <t>https://ibbi.gov.in/uploads/public_comments/DP - CIRP Proposals - 160226 - FF.pdf</t>
+  </si>
+  <si>
+    <t>Discussion_paper_Process_Division_February_2026_d4ab1036.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IBBI/Discussion Paper/2026/February/Discussion_paper_Process_Division_February_2026_d4ab1036.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,14 +85,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -104,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -114,58 +116,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -174,10 +158,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -215,71 +199,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -303,53 +285,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -359,7 +342,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -368,7 +351,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -377,7 +360,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -385,10 +368,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -417,7 +400,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -430,12 +413,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -453,25 +437,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="5" width="12.43357142857143" customWidth="1" bestFit="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,36 +470,39 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -43,31 +43,31 @@
     <t>Path</t>
   </si>
   <si>
-    <t>IBBI</t>
-  </si>
-  <si>
-    <t>Discussion Paper</t>
+    <t>Listed Companies</t>
+  </si>
+  <si>
+    <t>Circular-BSE</t>
   </si>
   <si>
     <t>2026</t>
   </si>
   <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>2026-02-16</t>
-  </si>
-  <si>
-    <t>Discussion paper – Process Division - February 2026</t>
-  </si>
-  <si>
-    <t>https://ibbi.gov.in/uploads/public_comments/DP - CIRP Proposals - 160226 - FF.pdf</t>
-  </si>
-  <si>
-    <t>Discussion_paper_Process_Division_February_2026_d4ab1036.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IBBI/Discussion Paper/2026/February/Discussion_paper_Process_Division_February_2026_d4ab1036.pdf</t>
+    <t>March</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>Update on single filing system through API-based integration between Stock Exchanges</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/markets/MarketInfo/DispNewNoticesCirculars.aspx?page=20260306-25</t>
+  </si>
+  <si>
+    <t>Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_996349dd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/March/Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_996349dd.pdf</t>
   </si>
 </sst>
 </file>

--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,10 +43,10 @@
     <t>Path</t>
   </si>
   <si>
-    <t>Listed Companies</t>
-  </si>
-  <si>
-    <t>Circular-BSE</t>
+    <t>IFSCA</t>
+  </si>
+  <si>
+    <t>Public Consultation</t>
   </si>
   <si>
     <t>2026</t>
@@ -58,16 +58,40 @@
     <t>2026-03-06</t>
   </si>
   <si>
-    <t>Update on single filing system through API-based integration between Stock Exchanges</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/markets/MarketInfo/DispNewNoticesCirculars.aspx?page=20260306-25</t>
-  </si>
-  <si>
-    <t>Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_996349dd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/March/Update_on_single_filing_system_through_API_based_integration_between_Stock_Excha_996349dd.pdf</t>
+    <t>Consultation Paper on IFSCA (Prohibition of Market Abuse in Securities Markets) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>Consultation Paper on the Regulatory Framework for Rights Issues by Listed Entities In the IFSC</t>
+  </si>
+  <si>
+    <t>Consultation Paper on the Regulatory Framework For Preferential Issues and Qualified Institutions Placements</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a820273d&amp;fileName=CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a82015fb&amp;fileName=CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a8200674&amp;fileName=CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
+  </si>
+  <si>
+    <t>CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
+  </si>
+  <si>
+    <t>CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
+  </si>
+  <si>
+    <t>CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
   </si>
 </sst>
 </file>
@@ -438,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -490,18 +514,78 @@
         <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>17</v>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
+    <hyperlink ref="G3" r:id="rId2"/>
+    <hyperlink ref="G4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="224">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,55 +43,649 @@
     <t>Path</t>
   </si>
   <si>
+    <t>SEBI</t>
+  </si>
+  <si>
+    <t>Listed Companies</t>
+  </si>
+  <si>
     <t>IFSCA</t>
   </si>
   <si>
+    <t>RBI</t>
+  </si>
+  <si>
+    <t>Circulars</t>
+  </si>
+  <si>
+    <t>Press Release</t>
+  </si>
+  <si>
+    <t>Consultation Paper</t>
+  </si>
+  <si>
+    <t>Circular-BSE</t>
+  </si>
+  <si>
     <t>Public Consultation</t>
   </si>
   <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>Master Directions</t>
+  </si>
+  <si>
     <t>2026</t>
   </si>
   <si>
     <t>March</t>
   </si>
   <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>Consultation Paper on IFSCA (Prohibition of Market Abuse in Securities Markets) Regulations, 2026</t>
-  </si>
-  <si>
-    <t>Consultation Paper on the Regulatory Framework for Rights Issues by Listed Entities In the IFSC</t>
-  </si>
-  <si>
-    <t>Consultation Paper on the Regulatory Framework For Preferential Issues and Qualified Institutions Placements</t>
-  </si>
-  <si>
-    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a820273d&amp;fileName=CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
-  </si>
-  <si>
-    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a82015fb&amp;fileName=CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
-  </si>
-  <si>
-    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a8200674&amp;fileName=CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
-  </si>
-  <si>
-    <t>CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
-  </si>
-  <si>
-    <t>CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
-  </si>
-  <si>
-    <t>CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_IFSCA__PROHIBITION_OF_MARKET_ABUSE_IN_SECURITIES_MARKETS__REGULATIONS__2026_20260306_0542.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_RIGHTS_ISSUES_BY_LISTED_ENTITIES_IN_THE_IFSC_20260306_0541.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/CONSULTATION_PAPER_ON_THE_REGULATORY_FRAMEWORK_FOR_PREFERENTIAL_ISSUES_AND_QUALIFIED_INSTITUTIONS_PLACEMENTS_20260306_0540.pdf</t>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>Ease of Doing Business – Relaxation in certification requirement for Persons Associated with Research Services (PARS) – Sales and other non-core services</t>
+  </si>
+  <si>
+    <t>Dr. Sadanand S. Date takes charge as Executive Director, SEBI</t>
+  </si>
+  <si>
+    <t>Ease of doing business - Roll out of NISM certification module for Persons Associated with Research Services – Sales and other non-core services</t>
+  </si>
+  <si>
+    <t>Consultation Paper on Ease of investing - Simplification of documentation requirement for transmission of securities and revision in threshold limits for simplified documentation.</t>
+  </si>
+  <si>
+    <t>Revised Norms for appointment of an independent third-party reviewer/ certifier for green debt security</t>
+  </si>
+  <si>
+    <t>Corrigendum to the Fee Circular dated March 02, 2026</t>
+  </si>
+  <si>
+    <t>Amendment to the Circular titled “Guidelines on Cyber Security and Cyber Resilience for Regulated Entities in IFSCs”</t>
+  </si>
+  <si>
+    <t>OFFICE OF ADMINISTRATOR (IFSCA) CONCLUDES OPEN HOUSE SERIES FOR REGULATED ENTITIES ON SEZ COMPLIANCE IN GIFT IFSC</t>
+  </si>
+  <si>
+    <t>Consultation paper on proposed IFSCA (Managing General Agents) Regulations, 2026</t>
+  </si>
+  <si>
+    <t>Public Consultation on draft guidelines on capital relief and prudential requirements for factoring transactions for FC/FUs</t>
+  </si>
+  <si>
+    <t>Implementation of Section 51A of UAPA, 1967: Updates to UNSC’s 1988 (2011) Taliban Sanctions List: Amendment of 22 Entries: UAPA Update 02 of 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (All India Financial Institutions (AIFIs) - Prudential Norms on Capital Adequacy) Second Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Payments Banks - Prudential Norms on Capital Adequacy) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Small Finance Banks - Prudential Norms on Capital Adequacy) Third Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Small Finance Banks – Prudential Norms on Declaration of Dividend) Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Regional Rural Banks – Prudential Norms on Declaration of Dividend) Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks - Prudential Norms on Capital Adequacy) Third Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Local Area Banks – Prudential Norms on Declaration of Dividends) Repeal Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Local Area Banks – Prudential Norms on Declaration of Dividend) Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Payment Banks – Prudential Norms on Declaration of Dividends) Repeal Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Small Finance Banks – Prudential Norms on Declaration of Dividends) Repeal Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Payments Banks – Prudential Norms on Declaration of Dividend) Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks – Prudential Norms on Declaration of Dividend and Remittance of Profit) Repeal Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks – Prudential Norms on Declaration of Dividend and Remittances of Profits) Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Setting Up of Wholly Owned Subsidiaries by Foreign Banks) Amendment Guidelines, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Standalone Primary Dealers) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Asset Reconstruction Companies) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Mortgage Guarantee Companies) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Core Investment Companies) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Housing Finance Companies) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Non-Banking Financial Companies - Concentration Risk Management) Second Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Non-Banking Financial Companies – Prudential Norms on Capital Adequacy) Second Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India – Bulletin Weekly Statistical Supplement – Extract</t>
+  </si>
+  <si>
+    <t>Open Market Operation (OMO) - Purchase of Government of India Securities held on Mar 13, 2026: Cut-Offs</t>
+  </si>
+  <si>
+    <t>Scheduled Banks’ Statement of Position in India as on February 28, 2026</t>
+  </si>
+  <si>
+    <t>Digital Payments Awareness Week 2026 - Launch of ‘Awareness Program on Digital Payments’ and Interaction with Payment Systems Operators (PSOs)</t>
+  </si>
+  <si>
+    <t>Directions under Section 35 A read with Section 56 of the Banking Regulation Act, 1949 – Kanaka Pattana Sahakara Bank Niyamita, Davangere</t>
+  </si>
+  <si>
+    <t>Directions under Section 35A read with Section 56 of the Banking Regulation Act, 1949 (AACS) - The Gujarat Rajya Karmachari Co-op. Bank Ltd., Ahmedabad, Gujarat</t>
+  </si>
+  <si>
+    <t>Directions under Section 35 A read with Section 56 of the Banking Regulation Act, 1949 – The U.P. Civil Secretariat Primary Cooperative Bank Limited, Lucknow</t>
+  </si>
+  <si>
+    <t>RBI announces OMO Purchase of Government of India Securities</t>
+  </si>
+  <si>
+    <t>Reserve Money and Money Supply for the fortnight ended February 28, 2026</t>
+  </si>
+  <si>
+    <t>RBI cancels Certificate of Registration of 36 NBFCs</t>
+  </si>
+  <si>
+    <t>9 NBFCs surrender their Certificate of Registration to the RBI</t>
+  </si>
+  <si>
+    <t>RBI issues Amendment Directions on ‘Counterparty Credit Risk - Add-on factors for computation of Potential Future Exposure’</t>
+  </si>
+  <si>
+    <t>RBI issues Directions on Prudential Norms on Declaration of Dividend and Remittance of Profit by Regulated Entities</t>
+  </si>
+  <si>
+    <t>RBI Issues Amendment Directions on ‘Clarification on Owned Fund / Tier 1 Capital computation for NBFCs / ARCs and applicability to Credit / Investment Concentration Norms’</t>
+  </si>
+  <si>
+    <t>Financial Action Task Force (FATF) High risk and other monitored jurisdictions – February 09-13, 2026</t>
+  </si>
+  <si>
+    <t>Open Market Operation (OMO) - Purchase of Government of India Securities held on Mar 09, 2026: Cut-Offs</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/mar-2026/1773222499084.pdf</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/mar-2026/1773409822331.pdf</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/mar-2026/1773234473571.pdf</t>
+  </si>
+  <si>
+    <t>https://www.sebi.gov.in/sebi_data/attachdocs/mar-2026/1773316942480.pdf</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/markets/MarketInfo/DownloadAttach.aspx?id=20260310-1&amp;attachedId=7d54ad6b-73db-4448-869c-667778a4459b</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a84dfe0b&amp;fileName=Corrigendum_to_the_Fee_Circular_dated_March_02__2026_20260313_0737.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a830d088&amp;fileName=Cyber_Security_Guidelines__Amendment__Circular_Final_100326_v04_20260310_0107.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a82de48e&amp;fileName=Press_Release_Open_House_Meeting_20260309_0644.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a84e295f&amp;fileName=2026_03_13_Public_Consultation_Draft___MGA_Regu_20260313_1112.pdf</t>
+  </si>
+  <si>
+    <t>https://ifsca.gov.in/CommonDirect/DownloadFile?id=d575554ec59b09e7fde503d3a83856e9&amp;fileName=Public_Consultation_Factoring_circular__march_11_approved_final_20260311_0554.pdf</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT242B412324D7EBC48FF92F214A5A6B609F8.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT24143B908C1E4C1428DA7D867B3663869FB.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT240B601FD00649E4E36ACB13E4048EAC882.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT2397FD7794FBE4849118C2951F082FE494F.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/391MD10032026DEA2C866625C478D9F4CC695FCA60B68.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/390MD10032026A83919BF58A2481BB8240A89F25F285E.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT2380F4C03D444554106809C8BA8756A3F3B.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/042378DF16EE12FD34DC2B3D51EC5BF0C941D.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/389MD100320260CC22242233B4A46883801B79C02FE8B.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/032365CB0CCE9D21A4C6C89E5371E29840D06.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/02235950499E11154436FB2DFE0A1D24119B4.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/388MD10032026C9C28BA2FD904454A24EE40607D82CC7.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/01NOT234DA82687BD4954E77A6939DEBE4ECE8D2.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/387MD1003202698CBFA3D29254532B33C97C231B6F7D8.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOT233ADFB78C1859445FD9A209C410270CDD5.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT232BFFE6E73E7134121A35401E7F71B2286.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT231EE31EBC9BA5E46C7931C6B075498CFDD.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT230695EB061609542BD81B3B2EF17638E77.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT229D210233127AB4C8588288EC24F9D4105.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT2288D371438FF1C4EA1BA535B4EA1E9623C.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT2279A25270BC9D4489C9965F39E306B6260.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT226EBFC6CBC4E134340A707A15512F0196B.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2262WSS66EF8720FA49493D86DAA594FF20E125.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR226148F32E653E9644C5A73D7FA8F051BCDD.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR22602684448CEC4543E58722602C63F77FE1.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR225808D9C9D30EAC41C9B4052B69E361B422.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR22570307AF6BA40A4FAD9F0631521D322A3F.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR225377486CF009794C40AB4E89C1ACF9AFE2.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2252A870C1B251CF4C20845DBF1B0AD2F2AF.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR225171A51B7997464971B0D07FB8680FE10E.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR22503C83AEF7CADA4F6D84B5FD49F5B1CE83.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2249F97CC95169FA46F997E808A0E4BA199B.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR224896FB35CB77874182B2DB27084EDF022F.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR22435DA6EC36894F46CE840C84438101DA1D.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2242A550A7F7901E46C4AFCE4DF192480C7A.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2241B67B41C954244C19993362BE5749B4EE.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2237E5A6228DB6324E778C8155B58B3430C3.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR223581ED033B16A9465DB33636AD134C748A.PDF</t>
+  </si>
+  <si>
+    <t>Ease_of_Doing_Business_Relaxation_in_certification_requirement_for_Persons_Assoc_fc2e94ab.pdf</t>
+  </si>
+  <si>
+    <t>Dr_Sadanand_S_Date_takes_charge_as_Executive_Director_SEBI_4a097abe.pdf</t>
+  </si>
+  <si>
+    <t>Ease_of_doing_business_Roll_out_of_NISM_certification_module_for_Persons_Associa_7188043c.pdf</t>
+  </si>
+  <si>
+    <t>Consultation_Paper_on_Ease_of_investing_Simplification_of_documentation_requirem_cd82902d.pdf</t>
+  </si>
+  <si>
+    <t>Revised_Norms_for_appointment_of_an_independent_third_party_reviewer_certifier_f_420e166e.pdf</t>
+  </si>
+  <si>
+    <t>Corrigendum_to_the_Fee_Circular_dated_March_02__2026_20260313_0737.pdf</t>
+  </si>
+  <si>
+    <t>Cyber_Security_Guidelines__Amendment__Circular_Final_100326_v04_20260310_0107.pdf</t>
+  </si>
+  <si>
+    <t>Press_Release_Open_House_Meeting_20260309_0644.pdf</t>
+  </si>
+  <si>
+    <t>2026_03_13_Public_Consultation_Draft___MGA_Regu_20260313_1112.pdf</t>
+  </si>
+  <si>
+    <t>Public_Consultation_Factoring_circular__march_11_approved_final_20260311_0554.pdf</t>
+  </si>
+  <si>
+    <t>Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1988_2011_Taliban_Sa_21f46a7d.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_All_India_Financial_Institutions_AIFIs_Prudential_Norms_on_5d552a46.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Payments_Banks_Prudential_Norms_on_Capital_Adequacy_Amendm_7d0cbb97.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Capital_Adequacy_T_a5e7c3d6.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Declaration_of_Div_46a9f162.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Regional_Rural_Banks_Prudential_Norms_on_Declaration_of_Di_ae21bb1a.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Capital_Adequacy_Thir_b568cfa6.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Local_Area_Banks_Prudential_Norms_on_Declaration_of_Divide_c339fe64.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Local_Area_Banks_Prudential_Norms_on_Declaration_of_Divide_c1ab3f66.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Payment_Banks_Prudential_Norms_on_Declaration_of_Dividends_579f9993.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Declaration_of_Div_de693961.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Payments_Banks_Prudential_Norms_on_Declaration_of_Dividend_aea99d6b.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Declaration_of_Divide_a0bfa0a1.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Declaration_of_Divide_c155ffb3.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Setting_Up_of_Wholly_Owned_Subsidiaries_by_Foreign_Banks_A_7d5e28d4.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Standalone_Primary_Dealers_Amendment_Directions_2026_80c57268.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Asset_Reconstruction_Companies_Amendment_Directions_2026_f661ca27.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Mortgage_Guarantee_Companies_Amendment_Directions_2026_03e3dc98.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Core_Investment_Companies_Amendment_Directions_2026_7079e7de.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Housing_Finance_Companies_Amendment_Directions_2026_009fee88.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Non_Banking_Financial_Companies_Concentration_Risk_Managem_b9f0be86.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Non_Banking_Financial_Companies_Prudential_Norms_on_Capita_9a7dcbc2.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Bulletin_Weekly_Statistical_Supplement_Extract_020ed489.pdf</t>
+  </si>
+  <si>
+    <t>Open_Market_Operation_OMO_Purchase_of_Government_of_India_Securities_held_on_Mar_8eb872ff.pdf</t>
+  </si>
+  <si>
+    <t>Scheduled_Banks_Statement_of_Position_in_India_as_on_February_28_2026_ed8bfa84.pdf</t>
+  </si>
+  <si>
+    <t>Digital_Payments_Awareness_Week_2026_Launch_of_Awareness_Program_on_Digital_Paym_05444c42.pdf</t>
+  </si>
+  <si>
+    <t>Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_0214cb6f.pdf</t>
+  </si>
+  <si>
+    <t>Directions_under_Section_35A_read_with_Section_56_of_the_Banking_Regulation_Act_11fdec92.pdf</t>
+  </si>
+  <si>
+    <t>Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_f0a97ffd.pdf</t>
+  </si>
+  <si>
+    <t>RBI_announces_OMO_Purchase_of_Government_of_India_Securities_ed7994eb.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Money_and_Money_Supply_for_the_fortnight_ended_February_28_2026_b42e051a.pdf</t>
+  </si>
+  <si>
+    <t>RBI_cancels_Certificate_of_Registration_of_36_NBFCs_46e83c21.pdf</t>
+  </si>
+  <si>
+    <t>9_NBFCs_surrender_their_Certificate_of_Registration_to_the_RBI_c74717d6.pdf</t>
+  </si>
+  <si>
+    <t>RBI_issues_Amendment_Directions_on_Counterparty_Credit_Risk_Add_on_factors_for_c_73692a47.pdf</t>
+  </si>
+  <si>
+    <t>RBI_issues_Directions_on_Prudential_Norms_on_Declaration_of_Dividend_and_Remitta_dd5a1e83.pdf</t>
+  </si>
+  <si>
+    <t>RBI_Issues_Amendment_Directions_on_Clarification_on_Owned_Fund_Tier_1_Capital_co_c3202ccd.pdf</t>
+  </si>
+  <si>
+    <t>Financial_Action_Task_Force_FATF_High_risk_and_other_monitored_jurisdictions_Feb_b409b718.pdf</t>
+  </si>
+  <si>
+    <t>Open_Market_Operation_OMO_Purchase_of_Government_of_India_Securities_held_on_Mar_3eceae84.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Circulars/2026/March/Ease_of_Doing_Business_Relaxation_in_certification_requirement_for_Persons_Assoc_fc2e94ab.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/March/Dr_Sadanand_S_Date_takes_charge_as_Executive_Director_SEBI_4a097abe.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Press Release/2026/March/Ease_of_doing_business_Roll_out_of_NISM_certification_module_for_Persons_Associa_7188043c.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/SEBI/Consultation Paper/2026/March/Consultation_Paper_on_Ease_of_investing_Simplification_of_documentation_requirem_cd82902d.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/March/Revised_Norms_for_appointment_of_an_independent_third_party_reviewer_certifier_f_420e166e.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Circulars/2026/March/Corrigendum_to_the_Fee_Circular_dated_March_02__2026_20260313_0737.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Circulars/2026/March/Cyber_Security_Guidelines__Amendment__Circular_Final_100326_v04_20260310_0107.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Press Release/2026/March/Press_Release_Open_House_Meeting_20260309_0644.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/2026_03_13_Public_Consultation_Draft___MGA_Regu_20260313_1112.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/IFSCA/Public Consultation/2026/March/Public_Consultation_Factoring_circular__march_11_approved_final_20260311_0554.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1988_2011_Taliban_Sa_21f46a7d.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_All_India_Financial_Institutions_AIFIs_Prudential_Norms_on_5d552a46.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Payments_Banks_Prudential_Norms_on_Capital_Adequacy_Amendm_7d0cbb97.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Capital_Adequacy_T_a5e7c3d6.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Declaration_of_Div_46a9f162.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Regional_Rural_Banks_Prudential_Norms_on_Declaration_of_Di_ae21bb1a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Capital_Adequacy_Thir_b568cfa6.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Local_Area_Banks_Prudential_Norms_on_Declaration_of_Divide_c339fe64.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Local_Area_Banks_Prudential_Norms_on_Declaration_of_Divide_c1ab3f66.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Payment_Banks_Prudential_Norms_on_Declaration_of_Dividends_579f9993.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Declaration_of_Div_de693961.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Payments_Banks_Prudential_Norms_on_Declaration_of_Dividend_aea99d6b.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Declaration_of_Divide_a0bfa0a1.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Declaration_of_Divide_c155ffb3.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Setting_Up_of_Wholly_Owned_Subsidiaries_by_Foreign_Banks_A_7d5e28d4.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Standalone_Primary_Dealers_Amendment_Directions_2026_80c57268.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Asset_Reconstruction_Companies_Amendment_Directions_2026_f661ca27.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Mortgage_Guarantee_Companies_Amendment_Directions_2026_03e3dc98.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Core_Investment_Companies_Amendment_Directions_2026_7079e7de.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Housing_Finance_Companies_Amendment_Directions_2026_009fee88.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Non_Banking_Financial_Companies_Concentration_Risk_Managem_b9f0be86.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/March/Reserve_Bank_of_India_Non_Banking_Financial_Companies_Prudential_Norms_on_Capita_9a7dcbc2.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Reserve_Bank_of_India_Bulletin_Weekly_Statistical_Supplement_Extract_020ed489.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Open_Market_Operation_OMO_Purchase_of_Government_of_India_Securities_held_on_Mar_8eb872ff.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Scheduled_Banks_Statement_of_Position_in_India_as_on_February_28_2026_ed8bfa84.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Digital_Payments_Awareness_Week_2026_Launch_of_Awareness_Program_on_Digital_Paym_05444c42.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_0214cb6f.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Directions_under_Section_35A_read_with_Section_56_of_the_Banking_Regulation_Act_11fdec92.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_f0a97ffd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/RBI_announces_OMO_Purchase_of_Government_of_India_Securities_ed7994eb.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Reserve_Money_and_Money_Supply_for_the_fortnight_ended_February_28_2026_b42e051a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/RBI_cancels_Certificate_of_Registration_of_36_NBFCs_46e83c21.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/9_NBFCs_surrender_their_Certificate_of_Registration_to_the_RBI_c74717d6.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/RBI_issues_Amendment_Directions_on_Counterparty_Credit_Risk_Add_on_factors_for_c_73692a47.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/RBI_issues_Directions_on_Prudential_Norms_on_Declaration_of_Dividend_and_Remitta_dd5a1e83.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/RBI_Issues_Amendment_Directions_on_Clarification_on_Owned_Fund_Tier_1_Capital_co_c3202ccd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Financial_Action_Task_Force_FATF_High_risk_and_other_monitored_jurisdictions_Feb_b409b718.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/March/Open_Market_Operation_OMO_Purchase_of_Government_of_India_Securities_held_on_Mar_3eceae84.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Master Directions/2026/March/Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Declaration_of_Divide_c155ffb3.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Master Directions/2026/March/Reserve_Bank_of_India_Small_Finance_Banks_Prudential_Norms_on_Declaration_of_Div_46a9f162.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Master Directions/2026/March/Reserve_Bank_of_India_Payments_Banks_Prudential_Norms_on_Declaration_of_Dividend_aea99d6b.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Master Directions/2026/March/Reserve_Bank_of_India_Local_Area_Banks_Prudential_Norms_on_Declaration_of_Divide_c1ab3f66.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Master Directions/2026/March/Reserve_Bank_of_India_Regional_Rural_Banks_Prudential_Norms_on_Declaration_of_Di_ae21bb1a.pdf</t>
   </si>
 </sst>
 </file>
@@ -462,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -499,28 +1093,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -528,28 +1122,28 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>124</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -557,28 +1151,1478 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" t="s">
+        <v>129</v>
+      </c>
+      <c r="I8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" t="s">
+        <v>133</v>
+      </c>
+      <c r="I12" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" t="s">
+        <v>135</v>
+      </c>
+      <c r="I14" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>136</v>
+      </c>
+      <c r="I15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" t="s">
+        <v>143</v>
+      </c>
+      <c r="I22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" t="s">
+        <v>48</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H24" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" t="s">
+        <v>146</v>
+      </c>
+      <c r="I25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" t="s">
+        <v>52</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>148</v>
+      </c>
+      <c r="I27" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" t="s">
+        <v>21</v>
+      </c>
+      <c r="E29" t="s">
+        <v>25</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F30" t="s">
+        <v>55</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" t="s">
+        <v>151</v>
+      </c>
+      <c r="I30" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E32" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H32" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>21</v>
+      </c>
+      <c r="E34" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H34" t="s">
+        <v>155</v>
+      </c>
+      <c r="I34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" t="s">
+        <v>156</v>
+      </c>
+      <c r="I35" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H36" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H37" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H38" t="s">
+        <v>159</v>
+      </c>
+      <c r="I38" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" t="s">
+        <v>65</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H40" t="s">
+        <v>161</v>
+      </c>
+      <c r="I40" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="s">
+        <v>21</v>
+      </c>
+      <c r="E41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" t="s">
+        <v>66</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H41" t="s">
+        <v>162</v>
+      </c>
+      <c r="I41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" t="s">
+        <v>21</v>
+      </c>
+      <c r="E42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H42" t="s">
+        <v>163</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H43" t="s">
+        <v>164</v>
+      </c>
+      <c r="I43" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" t="s">
+        <v>69</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H44" t="s">
+        <v>165</v>
+      </c>
+      <c r="I44" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" t="s">
+        <v>70</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" t="s">
+        <v>166</v>
+      </c>
+      <c r="I45" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D46" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H46" t="s">
+        <v>167</v>
+      </c>
+      <c r="I46" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E47" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" t="s">
+        <v>72</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H47" t="s">
+        <v>168</v>
+      </c>
+      <c r="I47" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H48" t="s">
+        <v>169</v>
+      </c>
+      <c r="I48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" t="s">
+        <v>26</v>
+      </c>
+      <c r="F49" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H49" t="s">
+        <v>170</v>
+      </c>
+      <c r="I49" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
         <v>19</v>
       </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>25</v>
+      <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" t="s">
+        <v>50</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H50" t="s">
+        <v>146</v>
+      </c>
+      <c r="I50" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E51" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s">
+        <v>137</v>
+      </c>
+      <c r="I51" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>19</v>
+      </c>
+      <c r="C52" t="s">
+        <v>20</v>
+      </c>
+      <c r="D52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
+        <v>48</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H52" t="s">
+        <v>144</v>
+      </c>
+      <c r="I52" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>19</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="s">
+        <v>21</v>
+      </c>
+      <c r="E53" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" t="s">
+        <v>45</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" t="s">
+        <v>141</v>
+      </c>
+      <c r="I53" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>19</v>
+      </c>
+      <c r="C54" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H54" t="s">
+        <v>138</v>
+      </c>
+      <c r="I54" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -586,6 +2630,56 @@
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
+    <hyperlink ref="G27" r:id="rId26"/>
+    <hyperlink ref="G28" r:id="rId27"/>
+    <hyperlink ref="G29" r:id="rId28"/>
+    <hyperlink ref="G30" r:id="rId29"/>
+    <hyperlink ref="G31" r:id="rId30"/>
+    <hyperlink ref="G32" r:id="rId31"/>
+    <hyperlink ref="G33" r:id="rId32"/>
+    <hyperlink ref="G34" r:id="rId33"/>
+    <hyperlink ref="G35" r:id="rId34"/>
+    <hyperlink ref="G36" r:id="rId35"/>
+    <hyperlink ref="G37" r:id="rId36"/>
+    <hyperlink ref="G38" r:id="rId37"/>
+    <hyperlink ref="G39" r:id="rId38"/>
+    <hyperlink ref="G40" r:id="rId39"/>
+    <hyperlink ref="G41" r:id="rId40"/>
+    <hyperlink ref="G42" r:id="rId41"/>
+    <hyperlink ref="G43" r:id="rId42"/>
+    <hyperlink ref="G44" r:id="rId43"/>
+    <hyperlink ref="G45" r:id="rId44"/>
+    <hyperlink ref="G46" r:id="rId45"/>
+    <hyperlink ref="G47" r:id="rId46"/>
+    <hyperlink ref="G48" r:id="rId47"/>
+    <hyperlink ref="G49" r:id="rId48"/>
+    <hyperlink ref="G50" r:id="rId49"/>
+    <hyperlink ref="G51" r:id="rId50"/>
+    <hyperlink ref="G52" r:id="rId51"/>
+    <hyperlink ref="G53" r:id="rId52"/>
+    <hyperlink ref="G54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="117">
   <si>
     <t>Verticals</t>
   </si>
@@ -46,57 +46,325 @@
     <t>Listed Companies</t>
   </si>
   <si>
+    <t>RBI</t>
+  </si>
+  <si>
     <t>Circular-BSE</t>
   </si>
   <si>
+    <t>Notifications</t>
+  </si>
+  <si>
+    <t>Press Release</t>
+  </si>
+  <si>
     <t>2026</t>
   </si>
   <si>
     <t>May</t>
   </si>
   <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>Extension of timeline for compliance with terms and conditions by_x000D_
-Debenture Trustees for carrying out activities outside the purview of_x000D_
-SEBI</t>
-  </si>
-  <si>
-    <t>XBRL based filing for Violations related to Code of Conduct (CoC) under SEBI PIT Regulations, 2015</t>
-  </si>
-  <si>
-    <t>Update of single filing system through API-based integration between Stock Exchanges</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260506-37/20260506-37.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260504-17/20260504-17.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260504-16/20260504-16.pdf</t>
-  </si>
-  <si>
-    <t>Extension_of_timeline_for_compliance_with_terms_and_conditions_by_Debenture_Trus_f80cf5c6.pdf</t>
-  </si>
-  <si>
-    <t>XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
-  </si>
-  <si>
-    <t>Update_of_single_filing_system_through_API_based_integration_between_Stock_Excha_0086bbc8.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Extension_of_timeline_for_compliance_with_terms_and_conditions_by_Debenture_Trus_f80cf5c6.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/XBRL_based_filing_for_Violations_related_to_Code_of_Conduct_CoC_under_SEBI_PIT_R_47394cc5.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Update_of_single_filing_system_through_API_based_integration_between_Stock_Excha_0086bbc8.pdf</t>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>Status of SPVs post conclusion or termination of Concession Agreement</t>
+  </si>
+  <si>
+    <t>Permitted use of fresh borrowings for InvITs where Net Borrowings exceeds forty-nine percent of the value of InvIT assets</t>
+  </si>
+  <si>
+    <t>Implementation of Section 51A of UAPA, 1967: Updates to UNSC’s 1267/ 1989 ISIL (Da'esh) &amp; Al-Qaida Sanctions List: Removal of 7 Entries</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Local Area Banks – Financial Statements: Presentation and Disclosures) Third Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks – Financial Statements: Presentation and Disclosures) Sixth Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks – Prudential Norms on Capital Adequacy) Sixth Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Regional Rural Banks - Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Rural Co-operative Banks – Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Urban Co-operative Banks – Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Local Area Banks - Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Payments Banks - Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Small Finance Banks - Classification, Valuation, and Operation of Investment Portfolio) Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>Reserve Bank of India (Commercial Banks - Classification, Valuation, and Operation of Investment Portfolio) Second Amendment Directions, 2026</t>
+  </si>
+  <si>
+    <t>623rdMeeting of Central Board of the Reserve Bank of India</t>
+  </si>
+  <si>
+    <t>Overseas Direct Investment for April 2026</t>
+  </si>
+  <si>
+    <t>RBI Issues Revised Draft Amendment Directions on ‘Conduct of Regulated Entities in Recovery of Loans and Engagement of Recovery Agents’</t>
+  </si>
+  <si>
+    <t>Reserve Money for the fortnight ended May 15, 2026</t>
+  </si>
+  <si>
+    <t>RBI invites comments on the draft “Reserve Bank of India (Capital Adequacy) Amendment Directions, 2026”</t>
+  </si>
+  <si>
+    <t>RBI cancels the licence of The Yashwant Co-operative Bank Ltd., Phaltan</t>
+  </si>
+  <si>
+    <t>RBI appoints Shri Gunveer Singh as new Executive Director</t>
+  </si>
+  <si>
+    <t>RBI issues Amendment Directions on ‘Investment Fluctuation Reserve’</t>
+  </si>
+  <si>
+    <t>Directions under Section 35 A read with Section 56 of the Banking Regulation Act, 1949 (AACS) – Nagar Sahakari Bank Ltd., Etawah</t>
+  </si>
+  <si>
+    <t>RBI publishes Payment System Report, December 2025</t>
+  </si>
+  <si>
+    <t>Review of Requirement of Counter-Cyclical Capital Buffer</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260520-10/20260520-10.pdf</t>
+  </si>
+  <si>
+    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260520-8/20260520-8.pdf</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOT93E8C6D7B847A74057AC3601A3D4142FA7.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOTI92D4EED82A29144087A855144A8885E2C3.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOTI919452D2826E4B401C8E0F5E19186A535D.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOTI90470E837E915C4182AE0C9D8C5718A66B.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOTI89E31D5A495AEC4A69ABF7E6EE6FA4824A.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/88NTC3010AFC82FF4B3CB22979352B28DA98.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/87NTB3DFD77D3B094FE4915E877FB7D97768.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/86NT6E591E9C4F874C7A82420CB56FA6DE84.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT850BEE108F04C3499693731F8AEF883AA6.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT84C533D9C069AF4F4AB19B3D56CB48CDBC.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NT83024DCDBEA7DE44C8AF2C0025AB1177DE.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR3117E9952A64D774CE1A6BB41D88292ADDA.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR303BF8E2C1E24B84705919D96490C498CA3.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR29893FBFE9E906944B2803A1943B6D0881D.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR2963AB47C801D3147F1A22A6B40B23C5B9E.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR29054365FF2FAA84B42AAE30506DBDC5302.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR28876FA31037FE8477D8D71E4CAADA188C8.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR285141EF01D43FA4FDA860BFC14207B014C.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR284A5D1DC0030864FB088AF60BB90A695C3.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR280C23DF07A213A4E5A9E9207F4D175E9A8.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR279B25DE9330A0C420482905E37E786D7CF.PDF</t>
+  </si>
+  <si>
+    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR278FAA54FA185234336815EDE8C281604C1.PDF</t>
+  </si>
+  <si>
+    <t>Status_of_SPVs_post_conclusion_or_termination_of_Concession_Agreement_58f075e0.pdf</t>
+  </si>
+  <si>
+    <t>Permitted_use_of_fresh_borrowings_for_InvITs_where_Net_Borrowings_exceeds_forty_5e010b4e.pdf</t>
+  </si>
+  <si>
+    <t>Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1267_1989_ISIL_Da_es_a82845a5.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Local_Area_Banks_Financial_Statements_Presentation_and_Dis_75c820f2.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Financial_Statements_Presentation_and_Dis_0999172c.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Capital_Adequacy_Sixt_006f7ebc.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Regional_Rural_Banks_Classification_Valuation_and_Operatio_0df81933.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Rural_Co_operative_Banks_Classification_Valuation_and_Oper_b47b3e63.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Urban_Co_operative_Banks_Classification_Valuation_and_Oper_c00d09a8.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Local_Area_Banks_Classification_Valuation_and_Operation_of_222268e8.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Payments_Banks_Classification_Valuation_and_Operation_of_I_60e977f6.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Small_Finance_Banks_Classification_Valuation_and_Operation_7d4eab1a.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Bank_of_India_Commercial_Banks_Classification_Valuation_and_Operation_of_0532ebe0.pdf</t>
+  </si>
+  <si>
+    <t>623rdMeeting_of_Central_Board_of_the_Reserve_Bank_of_India_f5319799.pdf</t>
+  </si>
+  <si>
+    <t>Overseas_Direct_Investment_for_April_2026_15ff6a0d.pdf</t>
+  </si>
+  <si>
+    <t>RBI_Issues_Revised_Draft_Amendment_Directions_on_Conduct_of_Regulated_Entities_i_26667172.pdf</t>
+  </si>
+  <si>
+    <t>Reserve_Money_for_the_fortnight_ended_May_15_2026_9505eafe.pdf</t>
+  </si>
+  <si>
+    <t>RBI_invites_comments_on_the_draft_Reserve_Bank_of_India_Capital_Adequacy_Amendme_a5a48ccb.pdf</t>
+  </si>
+  <si>
+    <t>RBI_cancels_the_licence_of_The_Yashwant_Co_operative_Bank_Ltd_Phaltan_bdf17290.pdf</t>
+  </si>
+  <si>
+    <t>RBI_appoints_Shri_Gunveer_Singh_as_new_Executive_Director_29710b8f.pdf</t>
+  </si>
+  <si>
+    <t>RBI_issues_Amendment_Directions_on_Investment_Fluctuation_Reserve_745055ff.pdf</t>
+  </si>
+  <si>
+    <t>Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_7567edfe.pdf</t>
+  </si>
+  <si>
+    <t>RBI_publishes_Payment_System_Report_December_2025_22221ccd.pdf</t>
+  </si>
+  <si>
+    <t>Review_of_Requirement_of_Counter_Cyclical_Capital_Buffer_37d848bf.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Status_of_SPVs_post_conclusion_or_termination_of_Concession_Agreement_58f075e0.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Permitted_use_of_fresh_borrowings_for_InvITs_where_Net_Borrowings_exceeds_forty_5e010b4e.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1267_1989_ISIL_Da_es_a82845a5.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Local_Area_Banks_Financial_Statements_Presentation_and_Dis_75c820f2.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Commercial_Banks_Financial_Statements_Presentation_and_Dis_0999172c.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Commercial_Banks_Prudential_Norms_on_Capital_Adequacy_Sixt_006f7ebc.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Regional_Rural_Banks_Classification_Valuation_and_Operatio_0df81933.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Rural_Co_operative_Banks_Classification_Valuation_and_Oper_b47b3e63.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Urban_Co_operative_Banks_Classification_Valuation_and_Oper_c00d09a8.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Local_Area_Banks_Classification_Valuation_and_Operation_of_222268e8.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Payments_Banks_Classification_Valuation_and_Operation_of_I_60e977f6.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Small_Finance_Banks_Classification_Valuation_and_Operation_7d4eab1a.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Reserve_Bank_of_India_Commercial_Banks_Classification_Valuation_and_Operation_of_0532ebe0.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/623rdMeeting_of_Central_Board_of_the_Reserve_Bank_of_India_f5319799.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Overseas_Direct_Investment_for_April_2026_15ff6a0d.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_Issues_Revised_Draft_Amendment_Directions_on_Conduct_of_Regulated_Entities_i_26667172.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Reserve_Money_for_the_fortnight_ended_May_15_2026_9505eafe.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_invites_comments_on_the_draft_Reserve_Bank_of_India_Capital_Adequacy_Amendme_a5a48ccb.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_cancels_the_licence_of_The_Yashwant_Co_operative_Bank_Ltd_Phaltan_bdf17290.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_appoints_Shri_Gunveer_Singh_as_new_Executive_Director_29710b8f.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_issues_Amendment_Directions_on_Investment_Fluctuation_Reserve_745055ff.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_7567edfe.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_publishes_Payment_System_Report_December_2025_22221ccd.pdf</t>
+  </si>
+  <si>
+    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Review_of_Requirement_of_Counter_Cyclical_Capital_Buffer_37d848bf.pdf</t>
   </si>
 </sst>
 </file>
@@ -467,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -504,28 +772,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -533,57 +801,666 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="H15" t="s">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
         <v>20</v>
       </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>39</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H20" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H21" t="s">
+        <v>88</v>
+      </c>
+      <c r="I21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H22" t="s">
+        <v>89</v>
+      </c>
+      <c r="I22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" t="s">
+        <v>92</v>
+      </c>
+      <c r="I25" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -591,6 +1468,27 @@
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
+    <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Searching_agent_output.xlsx
+++ b/data/Searching_agent_output.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="87">
   <si>
     <t>Verticals</t>
   </si>
@@ -43,15 +43,9 @@
     <t>Path</t>
   </si>
   <si>
-    <t>Listed Companies</t>
-  </si>
-  <si>
     <t>RBI</t>
   </si>
   <si>
-    <t>Circular-BSE</t>
-  </si>
-  <si>
     <t>Notifications</t>
   </si>
   <si>
@@ -64,27 +58,21 @@
     <t>May</t>
   </si>
   <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
     <t>2026-05-20</t>
   </si>
   <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-18</t>
-  </si>
-  <si>
-    <t>2026-05-21</t>
-  </si>
-  <si>
     <t>2026-05-19</t>
   </si>
   <si>
-    <t>Status of SPVs post conclusion or termination of Concession Agreement</t>
-  </si>
-  <si>
-    <t>Permitted use of fresh borrowings for InvITs where Net Borrowings exceeds forty-nine percent of the value of InvIT assets</t>
-  </si>
-  <si>
     <t>Implementation of Section 51A of UAPA, 1967: Updates to UNSC’s 1267/ 1989 ISIL (Da'esh) &amp; Al-Qaida Sanctions List: Removal of 7 Entries</t>
   </si>
   <si>
@@ -136,27 +124,6 @@
     <t>RBI cancels the licence of The Yashwant Co-operative Bank Ltd., Phaltan</t>
   </si>
   <si>
-    <t>RBI appoints Shri Gunveer Singh as new Executive Director</t>
-  </si>
-  <si>
-    <t>RBI issues Amendment Directions on ‘Investment Fluctuation Reserve’</t>
-  </si>
-  <si>
-    <t>Directions under Section 35 A read with Section 56 of the Banking Regulation Act, 1949 (AACS) – Nagar Sahakari Bank Ltd., Etawah</t>
-  </si>
-  <si>
-    <t>RBI publishes Payment System Report, December 2025</t>
-  </si>
-  <si>
-    <t>Review of Requirement of Counter-Cyclical Capital Buffer</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260520-10/20260520-10.pdf</t>
-  </si>
-  <si>
-    <t>https://www.bseindia.com/downloads/UploadDocs/Notices/20260520-8/20260520-8.pdf</t>
-  </si>
-  <si>
     <t>https://rbidocs.rbi.org.in/rdocs/notification/PDFs/NOT93E8C6D7B847A74057AC3601A3D4142FA7.PDF</t>
   </si>
   <si>
@@ -208,27 +175,6 @@
     <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR28876FA31037FE8477D8D71E4CAADA188C8.PDF</t>
   </si>
   <si>
-    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR285141EF01D43FA4FDA860BFC14207B014C.PDF</t>
-  </si>
-  <si>
-    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR284A5D1DC0030864FB088AF60BB90A695C3.PDF</t>
-  </si>
-  <si>
-    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR280C23DF07A213A4E5A9E9207F4D175E9A8.PDF</t>
-  </si>
-  <si>
-    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR279B25DE9330A0C420482905E37E786D7CF.PDF</t>
-  </si>
-  <si>
-    <t>https://rbidocs.rbi.org.in/rdocs/PressRelease/PDFs/PR278FAA54FA185234336815EDE8C281604C1.PDF</t>
-  </si>
-  <si>
-    <t>Status_of_SPVs_post_conclusion_or_termination_of_Concession_Agreement_58f075e0.pdf</t>
-  </si>
-  <si>
-    <t>Permitted_use_of_fresh_borrowings_for_InvITs_where_Net_Borrowings_exceeds_forty_5e010b4e.pdf</t>
-  </si>
-  <si>
     <t>Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1267_1989_ISIL_Da_es_a82845a5.pdf</t>
   </si>
   <si>
@@ -280,27 +226,6 @@
     <t>RBI_cancels_the_licence_of_The_Yashwant_Co_operative_Bank_Ltd_Phaltan_bdf17290.pdf</t>
   </si>
   <si>
-    <t>RBI_appoints_Shri_Gunveer_Singh_as_new_Executive_Director_29710b8f.pdf</t>
-  </si>
-  <si>
-    <t>RBI_issues_Amendment_Directions_on_Investment_Fluctuation_Reserve_745055ff.pdf</t>
-  </si>
-  <si>
-    <t>Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_7567edfe.pdf</t>
-  </si>
-  <si>
-    <t>RBI_publishes_Payment_System_Report_December_2025_22221ccd.pdf</t>
-  </si>
-  <si>
-    <t>Review_of_Requirement_of_Counter_Cyclical_Capital_Buffer_37d848bf.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Status_of_SPVs_post_conclusion_or_termination_of_Concession_Agreement_58f075e0.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/Listed Companies/Circular-BSE/2026/May/Permitted_use_of_fresh_borrowings_for_InvITs_where_Net_Borrowings_exceeds_forty_5e010b4e.pdf</t>
-  </si>
-  <si>
     <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Notifications/2026/May/Implementation_of_Section_51A_of_UAPA_1967_Updates_to_UNSCs_1267_1989_ISIL_Da_es_a82845a5.pdf</t>
   </si>
   <si>
@@ -350,21 +275,6 @@
   </si>
   <si>
     <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_cancels_the_licence_of_The_Yashwant_Co_operative_Bank_Ltd_Phaltan_bdf17290.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_appoints_Shri_Gunveer_Singh_as_new_Executive_Director_29710b8f.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_issues_Amendment_Directions_on_Investment_Fluctuation_Reserve_745055ff.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Directions_under_Section_35_A_read_with_Section_56_of_the_Banking_Regulation_Act_7567edfe.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/RBI_publishes_Payment_System_Report_December_2025_22221ccd.pdf</t>
-  </si>
-  <si>
-    <t>/Users/admin/Downloads/Tejomaya_pdfs/Akshayam Data/RBI/Press Release/2026/May/Review_of_Requirement_of_Counter_Cyclical_Capital_Buffer_37d848bf.pdf</t>
   </si>
 </sst>
 </file>
@@ -735,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -772,28 +682,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -801,666 +711,463 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="H3" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I10" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
         <v>15</v>
       </c>
-      <c r="E12" t="s">
-        <v>18</v>
-      </c>
       <c r="F12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
         <v>14</v>
       </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" t="s">
-        <v>18</v>
-      </c>
       <c r="F13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="I13" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="I16" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" t="s">
         <v>86</v>
-      </c>
-      <c r="I19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" t="s">
-        <v>39</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" t="s">
-        <v>87</v>
-      </c>
-      <c r="I20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H23" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H25" t="s">
-        <v>92</v>
-      </c>
-      <c r="I25" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1482,13 +1189,6 @@
     <hyperlink ref="G16" r:id="rId15"/>
     <hyperlink ref="G17" r:id="rId16"/>
     <hyperlink ref="G18" r:id="rId17"/>
-    <hyperlink ref="G19" r:id="rId18"/>
-    <hyperlink ref="G20" r:id="rId19"/>
-    <hyperlink ref="G21" r:id="rId20"/>
-    <hyperlink ref="G22" r:id="rId21"/>
-    <hyperlink ref="G23" r:id="rId22"/>
-    <hyperlink ref="G24" r:id="rId23"/>
-    <hyperlink ref="G25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
